--- a/reports/Debug-purgatory-20260105/For Winter Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260105/For Winter Ending (Actual)_Revenue.xlsx
@@ -79,19 +79,19 @@
     <t>account</t>
   </si>
   <si>
+    <t>T103</t>
+  </si>
+  <si>
+    <t>T100</t>
+  </si>
+  <si>
+    <t>T105</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
     <t>T110</t>
-  </si>
-  <si>
-    <t>T103</t>
-  </si>
-  <si>
-    <t>T105</t>
-  </si>
-  <si>
-    <t>T100</t>
   </si>
   <si>
     <t>department</t>
@@ -551,7 +551,7 @@
         <v>27</v>
       </c>
       <c r="D2" s="2">
-        <v>931.5800</v>
+        <v>315.0000</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -565,7 +565,7 @@
         <v>27</v>
       </c>
       <c r="D3" s="2">
-        <v>180.0000</v>
+        <v>2450264.1900</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -579,7 +579,7 @@
         <v>27</v>
       </c>
       <c r="D4" s="2">
-        <v>315.0000</v>
+        <v>52625.7200</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -593,7 +593,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="2">
-        <v>52625.7200</v>
+        <v>931.5800</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -607,7 +607,7 @@
         <v>27</v>
       </c>
       <c r="D6" s="2">
-        <v>2450264.1900</v>
+        <v>180.0000</v>
       </c>
     </row>
     <row r="7" spans="1:4">
